--- a/results/monthly_investor_report_2026-08-06.xlsx
+++ b/results/monthly_investor_report_2026-08-06.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -978,7 +978,7 @@
         <v>0.0493707647628267</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>636.773828896617</v>
+        <v>636.7738288966171</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>337.3727008712488</v>
@@ -1027,7 +1027,7 @@
         <v>205.0428176087989</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>186.1049942016601</v>
+        <v>186.1049942016602</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>0.9334174575978448</v>
@@ -1056,22 +1056,22 @@
         <v>0.1019676292204013</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10196.76292204013</v>
+        <v>10196.76292204012</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485935360435063</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>495.4967665792475</v>
+        <v>495.4967665792454</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>400.8248791526304</v>
+        <v>400.8248791526303</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>363.1375</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.9718707208701309</v>
+        <v>0.9718707208701279</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09651783980938428</v>
+        <v>0.0965178398093843</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9651.783980938428</v>
+        <v>9651.78398093843</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0535513188368701</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>516.8657613078291</v>
+        <v>516.8657613078292</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>382.4391287377838</v>
@@ -1147,13 +1147,13 @@
         <v>69.67315506435257</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>129.2054889307282</v>
+        <v>129.2054889307281</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>117.0125159007824</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.1302885333071543</v>
+        <v>0.130288533307153</v>
       </c>
       <c r="K24" s="10" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>50000.00000000001</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1506,7 +1506,7 @@
         <v>195.8999938964844</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.0031018113855404</v>
+        <v>-0.0031018113855402</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>0.0466708728798923</v>
@@ -1521,10 +1521,10 @@
         <v>205.0428176087989</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>212.4432543504554</v>
+        <v>212.4432543504555</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>186.1049942016601</v>
+        <v>186.1049942016602</v>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>-0.009829009969016899</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485935360435063</v>
       </c>
       <c r="G10" s="16" t="n">
         <v>0.1486668544898615</v>
@@ -1575,7 +1575,7 @@
         <v>378.4928609393433</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>400.8248791526304</v>
+        <v>400.8248791526303</v>
       </c>
       <c r="J10" s="15" t="n">
         <v>439.0779051287495</v>
@@ -1734,25 +1734,25 @@
         <v>105.3000030517578</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>-0.0616850558301536</v>
+        <v>-0.0616850558301534</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>-0.0093592552096705</v>
+        <v>-0.009359255209670601</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.0535268260817061</v>
+        <v>0.0535268260817058</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>98.80456648459479</v>
+        <v>98.8045664845948</v>
       </c>
       <c r="I13" s="18" t="n">
         <v>104.3144734496173</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>110.9363780015124</v>
+        <v>110.9363780015123</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>98.80456648459479</v>
+        <v>98.8045664845948</v>
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>19.05999946594238</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0432524986932348</v>
+        <v>-0.0432524986932347</v>
       </c>
       <c r="F14" s="22" t="n">
         <v>0.002557432846991</v>
@@ -1800,7 +1800,7 @@
         <v>0.06315792247529731</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>18.23560686394865</v>
+        <v>18.23560686394866</v>
       </c>
       <c r="I14" s="21" t="n">
         <v>19.10874413464022</v>
@@ -1854,7 +1854,7 @@
         <v>-0.0341997901255592</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1273843626077347</v>
+        <v>0.1273843626077345</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>289.0519869030868</v>
@@ -1974,7 +1974,7 @@
         <v>117.0125159007824</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>129.2054889307282</v>
+        <v>129.2054889307281</v>
       </c>
       <c r="J17" s="15" t="n">
         <v>135.0575066694285</v>
@@ -2019,7 +2019,7 @@
         <v>67.09999847412109</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.0666066214119836</v>
+        <v>-0.0666066214119837</v>
       </c>
       <c r="F18" s="25" t="n">
         <v>-0.0216543725047507</v>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2203,7 +2203,7 @@
         <v>0.2401157184185149</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.4602270876535832</v>
+        <v>0.4602270876535834</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>0.2304124079553751</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.0354122465978423</v>
+        <v>0.0354122465978425</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>-0.07375889410645679</v>
+        <v>-0.0737588941064567</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>-0.0229583630481745</v>
+        <v>-0.0229583630481744</v>
       </c>
       <c r="H5" s="16" t="n">
         <v>0.1578562564107331</v>
@@ -2303,7 +2303,7 @@
         <v>0.0202481395738857</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485935360435063</v>
       </c>
     </row>
     <row r="7">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-0.0268021624609804</v>
+        <v>-0.0268021624609806</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>-0.1121416154593406</v>
+        <v>-0.1121416154593408</v>
       </c>
       <c r="G9" s="19" t="n">
         <v>-0.1098901070553001</v>
@@ -2432,7 +2432,7 @@
         <v>0.0229823679178929</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>-0.0093592552096705</v>
+        <v>-0.009359255209670601</v>
       </c>
     </row>
     <row r="10">
@@ -2458,10 +2458,10 @@
         <v>-0.0052192266318432</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.1978114780161616</v>
+        <v>-0.1978114780161617</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>0.0381262980566652</v>
+        <v>0.0381262980566654</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>0.2620627924084371</v>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.0946807899751375</v>
+        <v>-0.09468078997513719</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>-0.1195033354919691</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.0295235758046596</v>
+        <v>0.0295235758046595</v>
       </c>
       <c r="K12" s="19" t="n">
         <v>-0.0089743807627755</v>
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0491070769676516</v>
+        <v>-0.0491070769676517</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>-0.07122094925188691</v>
+        <v>-0.071220949251887</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>-0.1771997464649704</v>
+        <v>-0.1771997464649705</v>
       </c>
       <c r="H13" s="16" t="n">
         <v>0.09552174833303501</v>
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="E14" s="27" t="n">
-        <v>-0.0506465993865901</v>
+        <v>-0.05064659938659</v>
       </c>
       <c r="F14" s="27" t="n">
         <v>-0.1190000152587891</v>
@@ -2647,7 +2647,7 @@
         <v>0.0210311854786991</v>
       </c>
       <c r="K14" s="27" t="n">
-        <v>0.0394097287801945</v>
+        <v>0.0394097287801946</v>
       </c>
     </row>
     <row r="15">
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0254119805740714</v>
+        <v>0.0254119805740715</v>
       </c>
       <c r="K16" s="27" t="n">
         <v>0.0357561195683878</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="E18" s="27" t="n">
-        <v>-0.0080971966300317</v>
+        <v>-0.0080971966300315</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>-0.1478260869565217</v>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0152928955505609</v>
+        <v>0.015292895550561</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>0.1120622093111625</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2052578638883636</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>-0.2979484965286054</v>
+        <v>-0.2979484965286055</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>-0.07856065964472959</v>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3411,8 +3411,8 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-08 03:15</t>
+          <t>Son Güncelleme: 2026-08-09 03:23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3510,7 +3510,7 @@
         <v>-2386.812482561385</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3540,7 +3540,7 @@
         <v>-64364.23179279291</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3564,13 +3564,13 @@
         <v>195.8999938964844</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>-0.00558378732749043</v>
+        <v>-0.005583787327490319</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>-16228.41092710616</v>
+        <v>-16228.4109271057</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3600,7 +3600,7 @@
         <v>-62904.35692547169</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3630,7 +3630,7 @@
         <v>197115.9711043495</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3654,13 +3654,13 @@
         <v>127.8000030517578</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>0</v>
+        <v>-7.275957614183426e-12</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>10100525.50440948</v>
+        <v>10158339.7140869</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.006917674013974</v>

--- a/results/monthly_investor_report_2026-08-06.xlsx
+++ b/results/monthly_investor_report_2026-08-06.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3412,7 +3412,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-08-09 03:23</t>
+          <t>Son Güncelleme: 2026-08-10 03:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3510,7 +3510,7 @@
         <v>-2386.812482561385</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3540,7 +3540,7 @@
         <v>-64364.23179279291</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3570,7 +3570,7 @@
         <v>-16228.4109271057</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3600,7 +3600,7 @@
         <v>-62904.35692547169</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3630,7 +3630,7 @@
         <v>197115.9711043495</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.006917674013974</v>
@@ -3660,7 +3660,7 @@
         <v>-7.275957614183426e-12</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>10158339.7140869</v>
+        <v>10216153.92376433</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.006917674013974</v>
